--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}fhs-1:年齢[x]または生まれ[x]を持つことができますが、両方ではありません / Can have age[x] or born[x], but not both {age.empty() or born.empty()}fhs-2:年齢[x]が存在する場合にのみ推定される可能性があります / Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}fhs-1:年齢[x]または生まれ[x]を持つことができますが、両方ではありません / Can have age[x] or born[x], but not both {age.empty() or born.empty()}fhs-2:年齢[x]が存在する場合にのみ推定される可能性があります / Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -535,7 +535,7 @@
     <t>FamilyMemberHistory.status</t>
   </si>
   <si>
-    <t>部分的|完了|エラーに入った|健康と知られていない / partial | completed | entered-in-error | health-unknown</t>
+    <t>部分的 | 完了 | エラー入力 | 不明 / partial | completed | entered-in-error | health-unknown</t>
   </si>
   <si>
     <t>特定の家族の家族歴史の記録のステータスを指定するコード。 / A code specifying the status of the record of the family history of a specific family member.</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-familymemberhistory.xlsx
@@ -789,10 +789,10 @@
     <t>FamilyMemberHistory.reasonCode</t>
   </si>
   <si>
-    <t>なぜ家族の歴史が演奏されたのですか？ / Why was family member history performed?</t>
-  </si>
-  <si>
-    <t>家族の歴史がコーディングされた形式またはテキスト形式で発生した理由について説明します。 / Describes why the family member history occurred in coded or textual form.</t>
+    <t>家族歴が作成された理由 / Why was family member history performed?</t>
+  </si>
+  <si>
+    <t>家族歴がコーディングされた形式またはテキスト形式で発生した理由について説明します。 / Describes why the family member history occurred in coded or textual form.</t>
   </si>
   <si>
     <t>テキストの理由は、ReasonCode.textを使用してキャプチャできます。 / Textual reasons can be captured using reasonCode.text.</t>
@@ -817,7 +817,7 @@
 </t>
   </si>
   <si>
-    <t>この家族の歴史イベントを正当化する条件、観察、アレルギーへの耐性、またはアンケートのサンキアが示すことを示します。 / Indicates a Condition, Observation, AllergyIntolerance, or QuestionnaireResponse that justifies this family member history event.</t>
+    <t>家族歴がコーディングされた形式またはテキスト形式で発生した理由について説明します。 / Indicates a Condition, Observation, AllergyIntolerance, or QuestionnaireResponse that justifies this family member history event.</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
